--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_01/sobol_total_indices.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_01/sobol_total_indices.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,37 +429,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>variavel</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>g_flexao_longarina</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>g_cisalhamento_longarina</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>g_flecha_longarina</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>g_flexao_tabuleiro</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>g_esp_longarina</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>g_esp_tabuleiro</t>
         </is>
@@ -460,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.077710011153248</v>
+        <v>1.084255341793407</v>
       </c>
       <c r="C2" t="n">
-        <v>1.161801065252575</v>
+        <v>1.39738250036164</v>
       </c>
       <c r="D2" t="n">
         <v>0.9989971747645225</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04586333861947045</v>
+        <v>0.04725551198679745</v>
       </c>
       <c r="F2" t="n">
         <v>-0.03717396361529457</v>
@@ -485,16 +497,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01873562498367176</v>
+        <v>0.02061668401414496</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03070384378450663</v>
+        <v>0.03476058999789255</v>
       </c>
       <c r="D3" t="n">
         <v>0.02690272950999995</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9320679309850415</v>
+        <v>0.9602200446310766</v>
       </c>
       <c r="F3" t="n">
         <v>-0.03717396361529457</v>
@@ -510,16 +522,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0202389522665718</v>
+        <v>0.02379721096489462</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04033095165789713</v>
+        <v>0.04976567801690623</v>
       </c>
       <c r="D4" t="n">
         <v>0.02690272950999995</v>
       </c>
       <c r="E4" t="n">
-        <v>1.452575154532845</v>
+        <v>1.537901382820817</v>
       </c>
       <c r="F4" t="n">
         <v>-0.03717396361529457</v>
@@ -535,16 +547,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02011840663708653</v>
+        <v>0.02339618961497991</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03828076979656625</v>
+        <v>0.124966257288037</v>
       </c>
       <c r="D5" t="n">
         <v>0.02690272950999995</v>
       </c>
       <c r="E5" t="n">
-        <v>11.32913568074023</v>
+        <v>11.71074452641327</v>
       </c>
       <c r="F5" t="n">
         <v>1.002937550486074</v>
@@ -560,16 +572,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01935038867867822</v>
+        <v>0.02114778937602912</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03447246728130438</v>
+        <v>0.03913432358518365</v>
       </c>
       <c r="D6" t="n">
         <v>0.02690272950999995</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04585051914444804</v>
+        <v>0.04724276936347804</v>
       </c>
       <c r="F6" t="n">
         <v>-0.03717396361529457</v>
